--- a/STM32_DualCore_Knowhow.xlsx
+++ b/STM32_DualCore_Knowhow.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="58">
+  <fonts count="64">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -355,8 +355,40 @@
       <color rgb="00005500"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Courier New"/>
+      <color rgb="00D4D4D4"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Courier New"/>
+      <b val="1"/>
+      <color rgb="00375623"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Courier New"/>
+      <color rgb="00888888"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001F3864"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Courier New"/>
+      <b val="1"/>
+      <color rgb="008B0000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00375623"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="38">
+  <fills count="39">
     <fill>
       <patternFill/>
     </fill>
@@ -543,6 +575,11 @@
         <fgColor rgb="FFF2CC80"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE8E8"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="12">
     <border>
@@ -686,7 +723,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1031,6 +1068,42 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="36" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="23" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="20" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="38" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4712,10 +4785,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A15:F15"/>
     <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A15:F15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4727,26 +4800,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>STM32 デュアルコア　－　Ethernet設計ガイド</t>
+          <t>STM32 デュアルコア　－　Ethernet / LWIP 設計ガイド</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
-      <c r="E1" s="3" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -4774,6 +4851,8 @@
           <t>優先度</t>
         </is>
       </c>
+      <c r="F2" s="76" t="inlineStr"/>
+      <c r="G2" s="76" t="inlineStr"/>
     </row>
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
@@ -5058,9 +5137,1788 @@
         </is>
       </c>
     </row>
+    <row r="13" ht="10" customHeight="1"/>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>LWIP 初期化フロー &amp; 実装手順（CM7側）</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="3" t="n"/>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="40" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B15" s="40" t="inlineStr">
+        <is>
+          <t>処理内容</t>
+        </is>
+      </c>
+      <c r="C15" s="40" t="inlineStr">
+        <is>
+          <t>実装コード / 設定</t>
+        </is>
+      </c>
+      <c r="D15" s="40" t="inlineStr">
+        <is>
+          <t>呼出し場所</t>
+        </is>
+      </c>
+      <c r="E15" s="40" t="inlineStr">
+        <is>
+          <t>完了確認方法</t>
+        </is>
+      </c>
+      <c r="F15" s="40" t="inlineStr">
+        <is>
+          <t>失敗時の症状</t>
+        </is>
+      </c>
+      <c r="G15" s="40" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="80" customHeight="1">
+      <c r="A16" s="58" t="inlineStr">
+        <is>
+          <t>① ETHペリフェラル
+初期化</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>HALレイヤでEthernetMACを初期化する。
+DMAデスクリプタ・MACアドレスを設定。</t>
+        </is>
+      </c>
+      <c r="C16" s="120" t="inlineStr">
+        <is>
+          <t>MX_ETH_Init();
+// CubeMXが自動生成
+// DMA Tx/Rx Descriptor設定含む</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>CM7のmain.c
+osKernelStart()より前</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>HAL_ETH_Init()がHAL_OKを返すか確認
+PHYリンクLEDが点灯</t>
+        </is>
+      </c>
+      <c r="F16" s="116" t="inlineStr">
+        <is>
+          <t>HAL_ETH_Init()がHAL_ERRORを返す
+PHYが応答しない</t>
+        </is>
+      </c>
+      <c r="G16" s="99" t="inlineStr">
+        <is>
+          <t>PHYアドレス(0x00〜0x1F)が
+HW設定と一致しているか確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="80" customHeight="1">
+      <c r="A17" s="58" t="inlineStr">
+        <is>
+          <t>② FreeRTOS
+カーネル起動</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>osKernelStart()でFreeRTOSスケジューラを起動。
+LWIPはFreeRTOS起動後にのみ初期化可能。</t>
+        </is>
+      </c>
+      <c r="C17" s="120" t="inlineStr">
+        <is>
+          <t>osKernelStart();
+// ← この後はタスク内で実行
+// ここより前にtcpip_init()禁止</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>CM7のmain.c
+FreeRTOS起動ポイント</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>osKernelStart()が返らない＝正常</t>
+        </is>
+      </c>
+      <c r="F17" s="116" t="inlineStr">
+        <is>
+          <t>osKernelStart()が即座に返る
+→スタック不足・タスク生成失敗</t>
+        </is>
+      </c>
+      <c r="G17" s="99" t="inlineStr">
+        <is>
+          <t>configTOTAL_HEAP_SIZEを
+確認・増加する</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="80" customHeight="1">
+      <c r="A18" s="58" t="inlineStr">
+        <is>
+          <t>③ tcpip_init()
+呼出し</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>LWIPのTCP/IPスタックとtcpip_threadを起動。
+必ずFreeRTOSタスク内で呼ぶこと。</t>
+        </is>
+      </c>
+      <c r="C18" s="120" t="inlineStr">
+        <is>
+          <t>// StartDefaultTask内
+void StartDefaultTask(void *arg){
+  tcpip_init(NULL, NULL);
+  // ← 最初に呼ぶ
+  MX_LWIP_Init();
+  ...
+}</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>StartDefaultTask()
+または専用InitTask内</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>tcpip_thread がタスクリストに
+表示される</t>
+        </is>
+      </c>
+      <c r="F18" s="116" t="inlineStr">
+        <is>
+          <t>LWIPタスクが生成されない
+netif_add()がフリーズ</t>
+        </is>
+      </c>
+      <c r="G18" s="99" t="inlineStr">
+        <is>
+          <t>tcpip_init()はFreeRTOS起動後
+最初に呼ぶ必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="80" customHeight="1">
+      <c r="A19" s="58" t="inlineStr">
+        <is>
+          <t>④ netif登録
+(MX_LWIP_Init)</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>ネットワークインターフェースをLWIPに登録。
+IPアドレス・MACアドレス・ドライバを紐付け。</t>
+        </is>
+      </c>
+      <c r="C19" s="120" t="inlineStr">
+        <is>
+          <t>// ethernetif.cのドライバ使用
+netif_add(&amp;gnetif,
+  &amp;ipaddr, &amp;netmask, &amp;gw,
+  NULL,
+  &amp;ethernetif_init,  // ドライバ
+  &amp;tcpip_input);     // 入力関数
+netif_set_default(&amp;gnetif);</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>MX_LWIP_Init()内
+（CubeMX自動生成）</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>netif_is_link_up()がtrueを返す</t>
+        </is>
+      </c>
+      <c r="F19" s="116" t="inlineStr">
+        <is>
+          <t>ethernetif_init()でHardFault
+→DMAバッファ配置問題</t>
+        </is>
+      </c>
+      <c r="G19" s="99" t="inlineStr">
+        <is>
+          <t>DMAバッファのアドレス・
+キャッシュ設定を確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="80" customHeight="1">
+      <c r="A20" s="58" t="inlineStr">
+        <is>
+          <t>⑤ IPアドレス取得
+(DHCP or 静的)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>DHCPでIPアドレスを自動取得、または静的IPを設定。
+DHCP使用時はタイムアウト処理が必須。</t>
+        </is>
+      </c>
+      <c r="C20" s="120" t="inlineStr">
+        <is>
+          <t>// DHCP使用の場合
+dhcp_start(&amp;gnetif);
+// タイムアウト監視(別タスク推奨)
+uint32_t timeout = 0;
+while(!dhcp_supplied_address(&amp;gnetif)){
+  osDelay(100);
+  if(++timeout &gt; 50){
+    // DHCP失敗→固定IPにフォールバック
+    netif_set_addr(&amp;gnetif,
+      &amp;static_ip, &amp;mask, &amp;gw);
+    break;
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>MX_LWIP_Init()後
+または専用DHCPタスク内</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>dhcp_supplied_address()が
+trueを返す
+gnetif.ip_addr が非ゼロ</t>
+        </is>
+      </c>
+      <c r="F20" s="116" t="inlineStr">
+        <is>
+          <t>IPアドレスが取得できない
+DHCPタイムアウトでシステム停止</t>
+        </is>
+      </c>
+      <c r="G20" s="99" t="inlineStr">
+        <is>
+          <t>DHCP失敗時の固定IPフォールバック
+を必ず実装すること</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="80" customHeight="1">
+      <c r="A21" s="58" t="inlineStr">
+        <is>
+          <t>⑥ netif有効化</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>ネットワークインターフェースをアップ状態にする。
+これ以降TCP/UDP通信が可能になる。</t>
+        </is>
+      </c>
+      <c r="C21" s="120" t="inlineStr">
+        <is>
+          <t>netif_set_up(&amp;gnetif);
+netif_set_link_up(&amp;gnetif);
+// PHYリンク状態に合わせて
+// netif_set_link_up/down()を
+// 動的に呼ぶことを推奨</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>IP取得完了後</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>netif_is_up()がtrue
+netif_is_link_up()がtrue</t>
+        </is>
+      </c>
+      <c r="F21" s="116" t="inlineStr">
+        <is>
+          <t>netif_set_up()後も通信できない
+→PHYリンクダウンの可能性</t>
+        </is>
+      </c>
+      <c r="G21" s="99" t="inlineStr">
+        <is>
+          <t>PHYリンク状態を定期監視する
+タスクを実装推奨</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>lwipopts.h 重要設定パラメータ</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="40" t="inlineStr">
+        <is>
+          <t>設定マクロ</t>
+        </is>
+      </c>
+      <c r="B24" s="40" t="inlineStr">
+        <is>
+          <t>推奨値</t>
+        </is>
+      </c>
+      <c r="C24" s="40" t="inlineStr">
+        <is>
+          <t>デフォルト値</t>
+        </is>
+      </c>
+      <c r="D24" s="40" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="E24" s="40" t="inlineStr">
+        <is>
+          <t>変更時の影響</t>
+        </is>
+      </c>
+      <c r="F24" s="40" t="inlineStr">
+        <is>
+          <t>STM32固有注意</t>
+        </is>
+      </c>
+      <c r="G24" s="40" t="inlineStr"/>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="98" t="inlineStr">
+        <is>
+          <t>NO_SYS</t>
+        </is>
+      </c>
+      <c r="B25" s="121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C25" s="122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>FreeRTOSと統合して使用する場合は0に設定。
+1にするとFreeRTOSなしのベアメタル動作になる。</t>
+        </is>
+      </c>
+      <c r="E25" s="99" t="inlineStr">
+        <is>
+          <t>1にするとtcpip_init()が不要になるが
+マルチタスク非対応になる</t>
+        </is>
+      </c>
+      <c r="F25" s="123" t="inlineStr">
+        <is>
+          <t>デュアルコアではFreeRTOS統合(0)が必須</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="98" t="inlineStr">
+        <is>
+          <t>LWIP_ETHERNET</t>
+        </is>
+      </c>
+      <c r="B26" s="124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>Ethernetサポートを有効化。</t>
+        </is>
+      </c>
+      <c r="E26" s="99" t="inlineStr">
+        <is>
+          <t>0にするとEthernetが無効</t>
+        </is>
+      </c>
+      <c r="F26" s="123" t="inlineStr">
+        <is>
+          <t>CubeMX生成時に自動設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="48" customHeight="1">
+      <c r="A27" s="98" t="inlineStr">
+        <is>
+          <t>MEM_SIZE</t>
+        </is>
+      </c>
+      <c r="B27" s="121" t="inlineStr">
+        <is>
+          <t>16 * 1024
+(16KB)</t>
+        </is>
+      </c>
+      <c r="C27" s="122" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>LWIPのヒープサイズ[bytes]。
+pbufやTCP接続状態の管理に使用。</t>
+        </is>
+      </c>
+      <c r="E27" s="99" t="inlineStr">
+        <is>
+          <t>小さすぎるとpbuf確保失敗で
+パケットドロップ多発</t>
+        </is>
+      </c>
+      <c r="F27" s="123" t="inlineStr">
+        <is>
+          <t>同時接続数 × 約2KBを目安に設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="98" t="inlineStr">
+        <is>
+          <t>MEMP_NUM_PBUF</t>
+        </is>
+      </c>
+      <c r="B28" s="124" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C28" s="125" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>参照カウント用pbufプールのサイズ。
+送信バッファとして使用。</t>
+        </is>
+      </c>
+      <c r="E28" s="99" t="inlineStr">
+        <is>
+          <t>不足すると送信待ちでスループット低下</t>
+        </is>
+      </c>
+      <c r="F28" s="123" t="inlineStr">
+        <is>
+          <t>ETH TX Descriptorの数と合わせる</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="98" t="inlineStr">
+        <is>
+          <t>MEMP_NUM_TCP_PCB</t>
+        </is>
+      </c>
+      <c r="B29" s="121" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C29" s="122" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>同時に保持できるTCP接続数（ESTABLISHED状態）。</t>
+        </is>
+      </c>
+      <c r="E29" s="99" t="inlineStr">
+        <is>
+          <t>不足すると新規接続が拒否される
+err_t = ERR_MEM が返る</t>
+        </is>
+      </c>
+      <c r="F29" s="123" t="inlineStr">
+        <is>
+          <t>アプリの最大同時接続数に合わせる</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="98" t="inlineStr">
+        <is>
+          <t>MEMP_NUM_TCP_PCB_LISTEN</t>
+        </is>
+      </c>
+      <c r="B30" s="124" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C30" s="125" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>LISTEN状態のTCPソケット数（待受ポート数）。</t>
+        </is>
+      </c>
+      <c r="E30" s="99" t="inlineStr">
+        <is>
+          <t>不足するとtcp_listen()がNULLを返す</t>
+        </is>
+      </c>
+      <c r="F30" s="123" t="inlineStr">
+        <is>
+          <t>使用するサーバポート数を設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="98" t="inlineStr">
+        <is>
+          <t>MEMP_NUM_UDP_PCB</t>
+        </is>
+      </c>
+      <c r="B31" s="121" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C31" s="122" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>同時に使用できるUDPソケット数。</t>
+        </is>
+      </c>
+      <c r="E31" s="99" t="inlineStr">
+        <is>
+          <t>不足するとudp_new()がNULLを返す</t>
+        </is>
+      </c>
+      <c r="F31" s="123" t="inlineStr">
+        <is>
+          <t>DHCP・DNS・mDNS等も内部でUDP使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="98" t="inlineStr">
+        <is>
+          <t>TCP_MSS</t>
+        </is>
+      </c>
+      <c r="B32" s="124" t="inlineStr">
+        <is>
+          <t>1460</t>
+        </is>
+      </c>
+      <c r="C32" s="125" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>TCP最大セグメントサイズ[bytes]。
+Ethernetの場合1460が最適値。</t>
+        </is>
+      </c>
+      <c r="E32" s="99" t="inlineStr">
+        <is>
+          <t>小さいと通信効率が低下
+大きすぎるとフラグメント発生</t>
+        </is>
+      </c>
+      <c r="F32" s="123" t="inlineStr">
+        <is>
+          <t>Ethernet使用時は必ず1460に設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="98" t="inlineStr">
+        <is>
+          <t>TCP_SND_BUF</t>
+        </is>
+      </c>
+      <c r="B33" s="121" t="inlineStr">
+        <is>
+          <t>4 * TCP_MSS
+(5840)</t>
+        </is>
+      </c>
+      <c r="C33" s="122" t="inlineStr">
+        <is>
+          <t>2 * TCP_MSS</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>TCP送信バッファサイズ[bytes]。
+大きいほどスループットが向上する。</t>
+        </is>
+      </c>
+      <c r="E33" s="99" t="inlineStr">
+        <is>
+          <t>小さいと連続送信時にACK待ちで停止</t>
+        </is>
+      </c>
+      <c r="F33" s="123" t="inlineStr">
+        <is>
+          <t>MEM_SIZEの範囲内で設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="98" t="inlineStr">
+        <is>
+          <t>TCP_WND</t>
+        </is>
+      </c>
+      <c r="B34" s="124" t="inlineStr">
+        <is>
+          <t>4 * TCP_MSS
+(5840)</t>
+        </is>
+      </c>
+      <c r="C34" s="125" t="inlineStr">
+        <is>
+          <t>4 * TCP_MSS</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>TCP受信ウィンドウサイズ[bytes]。
+相手に通知する受信バッファ量。</t>
+        </is>
+      </c>
+      <c r="E34" s="99" t="inlineStr">
+        <is>
+          <t>小さいと相手の送信速度が制限される</t>
+        </is>
+      </c>
+      <c r="F34" s="123" t="inlineStr">
+        <is>
+          <t>TCP_SND_BUFと同じかそれ以上を推奨</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="48" customHeight="1">
+      <c r="A35" s="98" t="inlineStr">
+        <is>
+          <t>LWIP_DHCP</t>
+        </is>
+      </c>
+      <c r="B35" s="121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>DHCPクライアント機能の有効化。</t>
+        </is>
+      </c>
+      <c r="E35" s="99" t="inlineStr">
+        <is>
+          <t>0にすると固定IPのみ使用可能</t>
+        </is>
+      </c>
+      <c r="F35" s="123" t="inlineStr">
+        <is>
+          <t>動的IP割当が不要な場合は0でRAM節約</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="48" customHeight="1">
+      <c r="A36" s="98" t="inlineStr">
+        <is>
+          <t>LWIP_DNS</t>
+        </is>
+      </c>
+      <c r="B36" s="124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>DNS名前解決機能の有効化。
+ホスト名でのサーバ接続に必要。</t>
+        </is>
+      </c>
+      <c r="E36" s="99" t="inlineStr">
+        <is>
+          <t>0にするとIPアドレスのみ接続可能</t>
+        </is>
+      </c>
+      <c r="F36" s="123" t="inlineStr">
+        <is>
+          <t>MEMP_NUM_UDP_PCBのカウントに含まれる</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="48" customHeight="1">
+      <c r="A37" s="98" t="inlineStr">
+        <is>
+          <t>LWIP_TCP_KEEPALIVE</t>
+        </is>
+      </c>
+      <c r="B37" s="121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>TCPキープアライブ機能の有効化。
+長時間通信のない接続の切断検出に使用。</t>
+        </is>
+      </c>
+      <c r="E37" s="99" t="inlineStr">
+        <is>
+          <t>0にすると死活確認ができず
+ゾンビ接続が残り続ける</t>
+        </is>
+      </c>
+      <c r="F37" s="123" t="inlineStr">
+        <is>
+          <t>サーバ運用では必ず有効化を推奨</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="48" customHeight="1">
+      <c r="A38" s="98" t="inlineStr">
+        <is>
+          <t>LWIP_SO_RCVTIMEO</t>
+        </is>
+      </c>
+      <c r="B38" s="124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C38" s="125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>ソケット受信タイムアウト機能の有効化。
+recv()のブロック時間を制限できる。</t>
+        </is>
+      </c>
+      <c r="E38" s="99" t="inlineStr">
+        <is>
+          <t>0にするとrecv()が無限ブロックする可能性</t>
+        </is>
+      </c>
+      <c r="F38" s="123" t="inlineStr">
+        <is>
+          <t>組込みでは必ず有効化してタイムアウト設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="48" customHeight="1">
+      <c r="A39" s="98" t="inlineStr">
+        <is>
+          <t>CHECKSUM_BY_HARDWARE</t>
+        </is>
+      </c>
+      <c r="B39" s="121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C39" s="122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>ETH MACのハードウェアチェックサム計算を使用。
+CPU負荷を大幅に削減できる。</t>
+        </is>
+      </c>
+      <c r="E39" s="99" t="inlineStr">
+        <is>
+          <t>0にするとソフトウェアでチェックサム計算
+CPU負荷が増加</t>
+        </is>
+      </c>
+      <c r="F39" s="123" t="inlineStr">
+        <is>
+          <t>STM32H7のETH MACはHWチェックサム対応
+ethernetif.cでも設定が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="48" customHeight="1">
+      <c r="A40" s="98" t="inlineStr">
+        <is>
+          <t>LWIP_STATS</t>
+        </is>
+      </c>
+      <c r="B40" s="124" t="inlineStr">
+        <is>
+          <t>1 (開発時)
+0 (本番)</t>
+        </is>
+      </c>
+      <c r="C40" s="125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>LWIP内部統計情報の収集を有効化。
+パケットドロップ数・メモリ使用量等を監視できる。</t>
+        </is>
+      </c>
+      <c r="E40" s="99" t="inlineStr">
+        <is>
+          <t>有効時はRAM使用量が増加</t>
+        </is>
+      </c>
+      <c r="F40" s="123" t="inlineStr">
+        <is>
+          <t>デバッグ時に有効化してstats_display()で確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="62" t="inlineStr">
+        <is>
+          <t>ethernetif.c カスタマイズ必須ポイント</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n"/>
+      <c r="E42" s="2" t="n"/>
+      <c r="F42" s="2" t="n"/>
+      <c r="G42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="29" t="inlineStr">
+        <is>
+          <t>関数 / 定義</t>
+        </is>
+      </c>
+      <c r="B43" s="29" t="inlineStr">
+        <is>
+          <t>デフォルト（要変更）</t>
+        </is>
+      </c>
+      <c r="C43" s="29" t="inlineStr">
+        <is>
+          <t>正しい実装</t>
+        </is>
+      </c>
+      <c r="D43" s="29" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+      <c r="E43" s="29" t="inlineStr">
+        <is>
+          <t>確認方法</t>
+        </is>
+      </c>
+      <c r="F43" s="29" t="inlineStr">
+        <is>
+          <t>影響</t>
+        </is>
+      </c>
+      <c r="G43" s="29" t="inlineStr"/>
+    </row>
+    <row r="44" ht="100" customHeight="1">
+      <c r="A44" s="126" t="inlineStr">
+        <is>
+          <t>ETH_RX_BUFFER_SIZE
+ETH_TX_BUFFER_SIZE</t>
+        </is>
+      </c>
+      <c r="B44" s="120" t="inlineStr">
+        <is>
+          <t>#define ETH_RX_BUFFER_SIZE 1536
+#define ETH_TX_BUFFER_SIZE 1536</t>
+        </is>
+      </c>
+      <c r="C44" s="120" t="inlineStr">
+        <is>
+          <t>// 1536以上に設定（Jumbo Frame不使用時）
+// 通常はデフォルトのままでOK
+// Ethernet最大フレーム=1518byte</t>
+        </is>
+      </c>
+      <c r="D44" s="99" t="inlineStr">
+        <is>
+          <t>バッファがフレームより小さいと受信が切れる</t>
+        </is>
+      </c>
+      <c r="E44" s="47" t="inlineStr">
+        <is>
+          <t>Wiresharkで受信フレームサイズを確認</t>
+        </is>
+      </c>
+      <c r="F44" s="116" t="inlineStr">
+        <is>
+          <t>受信データが途中で切れる</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="100" customHeight="1">
+      <c r="A45" s="126" t="inlineStr">
+        <is>
+          <t>Rx/TxバッファのMPU設定
+(★最重要)</t>
+        </is>
+      </c>
+      <c r="B45" s="120" t="inlineStr">
+        <is>
+          <t>// デフォルトは通常のメモリ
+// キャッシュが有効なまま</t>
+        </is>
+      </c>
+      <c r="C45" s="120" t="inlineStr">
+        <is>
+          <t>// MPUでNon-Cacheableに設定
+// または以下をRxコールバックで実行:
+SCB_InvalidateDCache_by_Addr(
+  (uint32_t*)RxBuf,
+  ETH_RX_BUFFER_SIZE);
+// TxはClean:
+SCB_CleanDCache_by_Addr(
+  (uint32_t*)TxBuf,
+  ETH_TX_BUFFER_SIZE);</t>
+        </is>
+      </c>
+      <c r="D45" s="99" t="inlineStr">
+        <is>
+          <t>DMAとCPUキャッシュの内容が
+一致しないとデータ化けが発生する</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>受信データの先頭数バイトを
+デバッガで確認（0x00やFFは異常）</t>
+        </is>
+      </c>
+      <c r="F45" s="116" t="inlineStr">
+        <is>
+          <t>受信データが全部0x00
+またはランダムな値になる</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="100" customHeight="1">
+      <c r="A46" s="126" t="inlineStr">
+        <is>
+          <t>ethernetif_input()
+受信処理</t>
+        </is>
+      </c>
+      <c r="B46" s="120" t="inlineStr">
+        <is>
+          <t>// CubeMXデフォルトはポーリング方式
+// or タスクで無限ループ</t>
+        </is>
+      </c>
+      <c r="C46" s="120" t="inlineStr">
+        <is>
+          <t>// ETH割込み駆動方式を推奨
+void HAL_ETH_RxCpltCallback(
+    ETH_HandleTypeDef *heth){
+  osSemaphoreRelease(RxSemHandle);
+}
+// EthIfTask内:
+void EthIfTask(void *arg){
+  while(1){
+    osSemaphoreAcquire(RxSemHandle,
+      portMAX_DELAY);
+    ethernetif_input(&amp;gnetif);
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D46" s="99" t="inlineStr">
+        <is>
+          <t>ポーリングではCPU占有率が高くなる
+割込み方式なら必要時のみCPUを使う</t>
+        </is>
+      </c>
+      <c r="E46" s="47" t="inlineStr">
+        <is>
+          <t>CPU使用率をvTaskGetRunTimeStats()
+で確認</t>
+        </is>
+      </c>
+      <c r="F46" s="116" t="inlineStr">
+        <is>
+          <t>ポーリングはCPU使用率が常に高い</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="100" customHeight="1">
+      <c r="A47" s="126" t="inlineStr">
+        <is>
+          <t>low_level_output()
+Tx送信後処理</t>
+        </is>
+      </c>
+      <c r="B47" s="120" t="inlineStr">
+        <is>
+          <t>// pbufを送信後そのまま
+// キャッシュCleanが未実装</t>
+        </is>
+      </c>
+      <c r="C47" s="120" t="inlineStr">
+        <is>
+          <t>// 送信前にDキャッシュをクリーン
+err_t low_level_output(
+    struct netif *netif,
+    struct pbuf *p) {
+  // pbufをDMAバッファにコピー
+  memcpy(TxBuf, p-&gt;payload, p-&gt;len);
+  // DキャッシュをClean
+  SCB_CleanDCache_by_Addr(
+    (uint32_t*)TxBuf, p-&gt;len);
+  // DMA送信開始
+  HAL_ETH_Transmit_IT(&amp;heth,
+    &amp;TxConfig);
+}</t>
+        </is>
+      </c>
+      <c r="D47" s="99" t="inlineStr">
+        <is>
+          <t>CPUキャッシュの内容がDRAMに
+フラッシュされないとDMAが古いデータを送信</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>Wiresharkで送信内容を確認</t>
+        </is>
+      </c>
+      <c r="F47" s="116" t="inlineStr">
+        <is>
+          <t>送信データが古い値や
+ゴミデータになる</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="100" customHeight="1">
+      <c r="A48" s="126" t="inlineStr">
+        <is>
+          <t>PHYリンク状態監視</t>
+        </is>
+      </c>
+      <c r="B48" s="120" t="inlineStr">
+        <is>
+          <t>// CubeMXデフォルトは
+// リンク変化を検出しない</t>
+        </is>
+      </c>
+      <c r="C48" s="120" t="inlineStr">
+        <is>
+          <t>// 定期監視タスクを実装
+void PhyMonitorTask(void *arg){
+  uint32_t regVal;
+  while(1){
+    HAL_ETH_ReadPHYRegister(
+      &amp;heth, PHY_ADDR,
+      PHY_BSR, &amp;regVal);
+    if(regVal &amp; PHY_LINKED_STATUS){
+      netif_set_link_up(&amp;gnetif);
+    } else {
+      netif_set_link_down(&amp;gnetif);
+    }
+    osDelay(200);
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D48" s="99" t="inlineStr">
+        <is>
+          <t>ケーブル抜き差しの検出が必要
+リンクダウン時にLWIPへ通知する</t>
+        </is>
+      </c>
+      <c r="E48" s="47" t="inlineStr">
+        <is>
+          <t>ケーブルを抜いてnetif_is_link_up()
+がfalseになるか確認</t>
+        </is>
+      </c>
+      <c r="F48" s="116" t="inlineStr">
+        <is>
+          <t>ケーブル再接続後に通信が
+復旧しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>LWIP API 使い方ガイド（TCP / UDP）</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n"/>
+      <c r="E50" s="2" t="n"/>
+      <c r="F50" s="2" t="n"/>
+      <c r="G50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="40" t="inlineStr">
+        <is>
+          <t>API種別</t>
+        </is>
+      </c>
+      <c r="B51" s="40" t="inlineStr">
+        <is>
+          <t>用途</t>
+        </is>
+      </c>
+      <c r="C51" s="40" t="inlineStr">
+        <is>
+          <t>主要API</t>
+        </is>
+      </c>
+      <c r="D51" s="40" t="inlineStr">
+        <is>
+          <t>実装例（抜粋）</t>
+        </is>
+      </c>
+      <c r="E51" s="40" t="inlineStr">
+        <is>
+          <t>注意点</t>
+        </is>
+      </c>
+      <c r="F51" s="40" t="inlineStr">
+        <is>
+          <t>スレッドセーフ</t>
+        </is>
+      </c>
+      <c r="G51" s="40" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="110" customHeight="1">
+      <c r="A52" s="58" t="inlineStr">
+        <is>
+          <t>TCPサーバ
+(RAW API)</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>ポーリング不要のコールバック方式。
+FreeRTOSなしでも動作。
+最も低レベルだがCPU効率が良い。</t>
+        </is>
+      </c>
+      <c r="C52" s="112" t="inlineStr">
+        <is>
+          <t>tcp_new()
+tcp_bind()
+tcp_listen()
+tcp_accept()
+tcp_recv()
+tcp_write()
+tcp_close()</t>
+        </is>
+      </c>
+      <c r="D52" s="120" t="inlineStr">
+        <is>
+          <t>struct tcp_pcb *pcb = tcp_new();
+tcp_bind(pcb, IP_ADDR_ANY, 80);
+pcb = tcp_listen(pcb);
+tcp_accept(pcb, accept_cb);
+// accept_cb内:
+tcp_recv(newpcb, recv_cb);
+// recv_cb内:
+tcp_write(pcb, data, len, 0);
+tcp_output(pcb);
+pbuf_free(p); // 必ず解放！</t>
+        </is>
+      </c>
+      <c r="E52" s="99" t="inlineStr">
+        <is>
+          <t>コールバックはtcpip_thread内で実行
+→FreeRTOSタスクから直接呼出し禁止
+tcpip_callback()経由で呼ぶこと
+pbufは必ず解放すること</t>
+        </is>
+      </c>
+      <c r="F52" s="87" t="inlineStr">
+        <is>
+          <t>✗ 非スレッドセーフ
+tcpip_callback()でラップ</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>最も軽量・高効率
+シンプルなサーバ実装に推奨</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="110" customHeight="1">
+      <c r="A53" s="58" t="inlineStr">
+        <is>
+          <t>TCPサーバ
+(Netconn API)</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>FreeRTOSタスクから直接呼べるブロッキングAPI。
+ソケットライクで使いやすい。
+RAW APIより使いやすいがメモリ消費大。</t>
+        </is>
+      </c>
+      <c r="C53" s="112" t="inlineStr">
+        <is>
+          <t>netconn_new()
+netconn_bind()
+netconn_listen()
+netconn_accept()
+netconn_recv()
+netconn_write()
+netconn_close()
+netconn_delete()</t>
+        </is>
+      </c>
+      <c r="D53" s="120" t="inlineStr">
+        <is>
+          <t>// FreeRTOSタスク内で使用OK
+struct netconn *conn, *client;
+conn = netconn_new(NETCONN_TCP);
+netconn_bind(conn,NULL,8080);
+netconn_listen(conn);
+while(1){
+  netconn_accept(conn,&amp;client);
+  // 受信
+  struct netbuf *buf;
+  netconn_recv(client, &amp;buf);
+  void *data; u16_t len;
+  netbuf_data(buf,&amp;data,&amp;len);
+  netconn_write(client,
+    resp, resplen,
+    NETCONN_COPY);
+  netbuf_delete(buf);
+  netconn_close(client);
+  netconn_delete(client);
+}</t>
+        </is>
+      </c>
+      <c r="E53" s="99" t="inlineStr">
+        <is>
+          <t>LWIP_NETCONN=1 が必要(lwipopts.h)
+MEMP_NUM_NETCONN の数に制限あり
+netbufは必ずnetbuf_delete()で解放</t>
+        </is>
+      </c>
+      <c r="F53" s="64" t="inlineStr">
+        <is>
+          <t>✓ スレッドセーフ
+FreeRTOSタスクから直接呼出し可能</t>
+        </is>
+      </c>
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>FreeRTOS使用時の推奨API
+コードが読みやすい</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="110" customHeight="1">
+      <c r="A54" s="58" t="inlineStr">
+        <is>
+          <t>UDPソケット
+(RAW API)</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>コネクションレスの軽量通信。
+センサデータ送信・ブロードキャスト・
+DHCP/DNS等の基盤プロトコルでも使用。</t>
+        </is>
+      </c>
+      <c r="C54" s="112" t="inlineStr">
+        <is>
+          <t>udp_new()
+udp_bind()
+udp_connect()
+udp_send()
+udp_sendto()
+udp_recv()
+udp_remove()</t>
+        </is>
+      </c>
+      <c r="D54" s="120" t="inlineStr">
+        <is>
+          <t>struct udp_pcb *pcb = udp_new();
+udp_bind(pcb, IP_ADDR_ANY, 5000);
+udp_recv(pcb, udp_recv_cb, NULL);
+// 送信例
+struct pbuf *p;
+p = pbuf_alloc(PBUF_TRANSPORT,
+  dataLen, PBUF_RAM);
+memcpy(p-&gt;payload, data, dataLen);
+udp_sendto(pcb, p,
+  &amp;dest_ip, dest_port);
+pbuf_free(p); // 送信後解放</t>
+        </is>
+      </c>
+      <c r="E54" s="99" t="inlineStr">
+        <is>
+          <t>pbufの確保・解放を必ず対で実装
+RAW APIはtcpip_thread内でのみ安全</t>
+        </is>
+      </c>
+      <c r="F54" s="87" t="inlineStr">
+        <is>
+          <t>✗ 非スレッドセーフ
+tcpip_callback()でラップ</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>センサデータ送信等の
+高頻度・低レイテンシ通信に適する</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="110" customHeight="1">
+      <c r="A55" s="58" t="inlineStr">
+        <is>
+          <t>HTTPサーバ
+(httpd)</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>LWIP内蔵の簡易HTTPサーバ機能。
+WebブラウザからSTM32を監視・制御できる。
+lwipopts.hでLWIP_HTTPD=1を設定。</t>
+        </is>
+      </c>
+      <c r="C55" s="112" t="inlineStr">
+        <is>
+          <t>httpd_init()
+http_set_ssi_handler()
+http_set_cgi_handler()
+(ファイルはfsdata.cに組込み)</t>
+        </is>
+      </c>
+      <c r="D55" s="120" t="inlineStr">
+        <is>
+          <t>// 初期化
+httpd_init();
+// SSI(Server Side Include)ハンドラ
+const char* ssi_tags[] =
+  {"temp","status"};
+http_set_ssi_handler(
+  ssi_handler, ssi_tags, 2);
+// ssi_handler内:
+u16_t ssi_handler(int idx,
+    char *pcInsert, int len){
+  if(idx==0) // temp
+    return snprintf(pcInsert,
+      len, "%d", temperature);
+}</t>
+        </is>
+      </c>
+      <c r="E55" s="99" t="inlineStr">
+        <is>
+          <t>FSデータはmakefsdata.exeで生成
+httpd.cの内部バッファサイズに注意
+ファイルサイズが大きいとFlash消費大</t>
+        </is>
+      </c>
+      <c r="F55" s="64" t="inlineStr">
+        <is>
+          <t>✓ LWIPが内部管理</t>
+        </is>
+      </c>
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>デバッグWebUIや
+ステータス監視に便利</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="110" customHeight="1">
+      <c r="A56" s="58" t="inlineStr">
+        <is>
+          <t>エラーハンドリング
+共通事項</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>LWIP APIはerr_t型でエラーを返す。
+全APIの戻り値を確認し
+エラー処理を必ず実装すること。</t>
+        </is>
+      </c>
+      <c r="C56" s="112" t="inlineStr">
+        <is>
+          <t>ERR_OK   = 0  // 成功
+ERR_MEM  = -1 // メモリ不足
+ERR_BUF  = -2 // バッファエラー
+ERR_TIMEOUT=-3 // タイムアウト
+ERR_RTE  = -4 // ルーティングなし
+ERR_INPROGRESS=-5 // 処理中
+ERR_VAL  = -6 // 不正な値
+ERR_CONN = -11 // 接続失敗
+ERR_CLSD = -13 // 接続クローズ済</t>
+        </is>
+      </c>
+      <c r="D56" s="120" t="inlineStr">
+        <is>
+          <t>err_t err = tcp_bind(pcb,
+  IP_ADDR_ANY, 80);
+if(err != ERR_OK){
+  // ポートが既に使用中等
+  tcp_close(pcb);
+  // ログ出力・リトライ処理
+  Error_Handler();
+}</t>
+        </is>
+      </c>
+      <c r="E56" s="99" t="inlineStr">
+        <is>
+          <t>ERR_MEMが多発する場合は
+MEM_SIZE / MEMP_NUM_*を増やす
+LWIP_STATSで統計を確認</t>
+        </is>
+      </c>
+      <c r="F56" s="87" t="inlineStr">
+        <is>
+          <t>必ず戻り値チェック</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>stats_display()でメモリ
+枯渇を確認できる</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="28" customHeight="1">
+      <c r="A58" s="62" t="inlineStr">
+        <is>
+          <t>LWIP トラブルシューティング</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n"/>
+      <c r="E58" s="2" t="n"/>
+      <c r="F58" s="2" t="n"/>
+      <c r="G58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="29" t="inlineStr">
+        <is>
+          <t>症状</t>
+        </is>
+      </c>
+      <c r="B59" s="29" t="inlineStr">
+        <is>
+          <t>確認ポイント</t>
+        </is>
+      </c>
+      <c r="C59" s="29" t="inlineStr">
+        <is>
+          <t>原因</t>
+        </is>
+      </c>
+      <c r="D59" s="29" t="inlineStr">
+        <is>
+          <t>対策</t>
+        </is>
+      </c>
+      <c r="E59" s="29" t="inlineStr">
+        <is>
+          <t>確認コマンド/方法</t>
+        </is>
+      </c>
+      <c r="F59" s="29" t="inlineStr"/>
+      <c r="G59" s="29" t="inlineStr"/>
+    </row>
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" s="127" t="inlineStr">
+        <is>
+          <t>通信は確立するが
+データが化ける
+(0x00 / ランダム値)</t>
+        </is>
+      </c>
+      <c r="B60" s="47" t="inlineStr">
+        <is>
+          <t>ethernetif.cのキャッシュ操作
+MPU設定のNon-Cacheable確認</t>
+        </is>
+      </c>
+      <c r="C60" s="99" t="inlineStr">
+        <is>
+          <t>DMAバッファのキャッシュコヒーレンシ問題
+CPUキャッシュとDMAのデータが不一致</t>
+        </is>
+      </c>
+      <c r="D60" s="128" t="inlineStr">
+        <is>
+          <t>RxコールバックでSCB_InvalidateDCache_by_Addr()
+Tx前にSCB_CleanDCache_by_Addr()
+またはMPUでNon-Cacheable設定</t>
+        </is>
+      </c>
+      <c r="E60" s="129" t="inlineStr">
+        <is>
+          <t>Wiresharkで受信パケットを確認
+デバッガでRxバッファ内容を直接確認</t>
+        </is>
+      </c>
+      <c r="F60" s="47" t="inlineStr"/>
+      <c r="G60" s="47" t="inlineStr"/>
+    </row>
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" s="130" t="inlineStr">
+        <is>
+          <t>IPアドレスが
+取得できない
+(DHCP失敗)</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>PHYリンクアップ確認
+DHCPサーバの存在確認
+netif_set_link_up()の呼出し確認</t>
+        </is>
+      </c>
+      <c r="C61" s="99" t="inlineStr">
+        <is>
+          <t>netif_set_link_up()未呼出し
+PHYがリンクアップしていない
+DHCPサーバが存在しない</t>
+        </is>
+      </c>
+      <c r="D61" s="128" t="inlineStr">
+        <is>
+          <t>netif_set_up()とnetif_set_link_up()を両方呼ぶ
+PHYレジスタでリンク状態を確認
+固定IPへのフォールバックを実装</t>
+        </is>
+      </c>
+      <c r="E61" s="131" t="inlineStr">
+        <is>
+          <t>HAL_ETH_ReadPHYRegister()でPHY_BSR確認
+PHY_LINKED_STATUSビット=1がリンクアップ</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="inlineStr"/>
+      <c r="G61" s="9" t="inlineStr"/>
+    </row>
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" s="127" t="inlineStr">
+        <is>
+          <t>TCP接続が頻繁に
+タイムアウト/切断</t>
+        </is>
+      </c>
+      <c r="B62" s="47" t="inlineStr">
+        <is>
+          <t>タスク優先度の確認
+lwipopts.hのバッファサイズ確認
+CPU負荷の確認</t>
+        </is>
+      </c>
+      <c r="C62" s="99" t="inlineStr">
+        <is>
+          <t>EthIfTaskの優先度が低くパケット処理遅延
+TCP_WNDが小さすぎて輻輳制御が効きすぎ
+CM4タスクがCM7のEth処理をブロック</t>
+        </is>
+      </c>
+      <c r="D62" s="128" t="inlineStr">
+        <is>
+          <t>EthIfTaskの優先度をAboveNormal(6)以上に
+TCP_WNDとTCP_SND_BUFを4×TCP_MSSに
+CM7のEth関連タスク優先度を見直す</t>
+        </is>
+      </c>
+      <c r="E62" s="129" t="inlineStr">
+        <is>
+          <t>vTaskGetRunTimeStats()でCPU使用率確認
+WiresharkでTCP Retransmissionを確認</t>
+        </is>
+      </c>
+      <c r="F62" s="47" t="inlineStr"/>
+      <c r="G62" s="47" t="inlineStr"/>
+    </row>
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" s="130" t="inlineStr">
+        <is>
+          <t>メモリ不足エラー
+(ERR_MEM多発)</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>lwipopts.hのMEM_SIZE・MEMP_NUM_*確認
+ヒープ残量確認
+同時接続数確認</t>
+        </is>
+      </c>
+      <c r="C63" s="99" t="inlineStr">
+        <is>
+          <t>MEM_SIZEが小さすぎる
+MEMP_NUM_TCP_PCBが同時接続数より少ない
+pbufが解放されないメモリリーク</t>
+        </is>
+      </c>
+      <c r="D63" s="128" t="inlineStr">
+        <is>
+          <t>MEM_SIZEを倍に増やして試す
+MEMP_NUM_TCP_PCBを同時接続数+余裕で設定
+pbuf_free()漏れをコードレビュー</t>
+        </is>
+      </c>
+      <c r="E63" s="131" t="inlineStr">
+        <is>
+          <t>LWIP_STATS=1 + stats_display()で
+メモリ使用状況を確認</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr"/>
+      <c r="G63" s="9" t="inlineStr"/>
+    </row>
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" s="127" t="inlineStr">
+        <is>
+          <t>tcpip_init()後に
+フリーズする</t>
+        </is>
+      </c>
+      <c r="B64" s="47" t="inlineStr">
+        <is>
+          <t>FreeRTOSヒープ残量確認
+tcpip_thread_stacksize設定確認
+タスク生成順序確認</t>
+        </is>
+      </c>
+      <c r="C64" s="99" t="inlineStr">
+        <is>
+          <t>tcpip_threadのスタック不足
+FreeRTOSヒープ不足でタスク生成失敗
+osKernelStart()より前にtcpip_init()を呼んでいる</t>
+        </is>
+      </c>
+      <c r="D64" s="128" t="inlineStr">
+        <is>
+          <t>configTOTAL_HEAP_SIZEを増やす
+TCPIP_THREAD_STACKSIZEを1024以上に
+tcpip_init()はFreeRTOS起動後のタスク内で呼ぶ</t>
+        </is>
+      </c>
+      <c r="E64" s="129" t="inlineStr">
+        <is>
+          <t>xPortGetFreeHeapSize()でヒープ残量確認
+vApplicationMallocFailedHook()を実装</t>
+        </is>
+      </c>
+      <c r="F64" s="47" t="inlineStr"/>
+      <c r="G64" s="47" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="7">
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A58:G58"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A50:G50"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
